--- a/database/event/4177/event_4177_evp_summary.xlsx
+++ b/database/event/4177/event_4177_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5623</v>
+        <v>7.9416</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1856</v>
+        <v>3.3454</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6336</v>
+        <v>2.72</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5623</v>
+        <v>7.9416</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2257</v>
+        <v>3.6051</v>
       </c>
       <c r="G2" t="n">
         <v>4.3366</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2257</v>
+        <v>3.6051</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6146</v>
+        <v>2.922</v>
       </c>
       <c r="J2" t="n">
         <v>4.3366</v>
@@ -529,7 +529,7 @@
         <v>138</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9512</v>
+        <v>7.258599999999999</v>
       </c>
       <c r="N2" t="n">
         <v>312</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8142</v>
+        <v>6.8171</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8705</v>
+        <v>2.8717</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3314</v>
+        <v>2.272</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8142</v>
+        <v>6.8171</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1934</v>
+        <v>4.3848</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6208</v>
+        <v>2.4323</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3104</v>
+        <v>5.0807</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4937</v>
+        <v>4.118</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6208</v>
+        <v>2.4323</v>
       </c>
       <c r="K3" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L3" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1145</v>
+        <v>6.5503</v>
       </c>
       <c r="N3" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6769</v>
+        <v>6.8142</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8126</v>
+        <v>2.8705</v>
       </c>
       <c r="D4" t="n">
-        <v>2.276</v>
+        <v>2.2709</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6769</v>
+        <v>6.8142</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2446</v>
+        <v>4.1934</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4323</v>
+        <v>2.6208</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5165</v>
+        <v>4.3104</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6607</v>
+        <v>3.4937</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4323</v>
+        <v>2.6208</v>
       </c>
       <c r="K4" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L4" t="n">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="M4" t="n">
-        <v>6.093</v>
+        <v>6.1145</v>
       </c>
       <c r="N4" t="n">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.6561</v>
+        <v>6.7827</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8039</v>
+        <v>2.8572</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2676</v>
+        <v>2.2583</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6561</v>
+        <v>6.7827</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2357</v>
+        <v>4.3623</v>
       </c>
       <c r="G5" t="n">
         <v>2.4204</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4807</v>
+        <v>4.9899</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6318</v>
+        <v>4.0444</v>
       </c>
       <c r="J5" t="n">
         <v>2.4204</v>
@@ -667,7 +667,7 @@
         <v>153</v>
       </c>
       <c r="M5" t="n">
-        <v>6.0522</v>
+        <v>6.4648</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4016</v>
+        <v>5.4513</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2754</v>
+        <v>2.2963</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7608</v>
+        <v>1.7279</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4016</v>
+        <v>5.4513</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9822</v>
+        <v>3.0319</v>
       </c>
       <c r="G6" t="n">
         <v>2.4194</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9822</v>
+        <v>3.0319</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9822</v>
+        <v>3.0319</v>
       </c>
       <c r="J6" t="n">
         <v>2.4194</v>
@@ -713,7 +713,7 @@
         <v>136</v>
       </c>
       <c r="M6" t="n">
-        <v>5.4016</v>
+        <v>5.4513</v>
       </c>
       <c r="N6" t="n">
         <v>300</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.24</v>
+        <v>5.2185</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2073</v>
+        <v>2.1983</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6955</v>
+        <v>1.6351</v>
       </c>
       <c r="E7" t="n">
-        <v>5.24</v>
+        <v>5.2185</v>
       </c>
       <c r="F7" t="n">
-        <v>4.3644</v>
+        <v>4.3429</v>
       </c>
       <c r="G7" t="n">
         <v>0.8756</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5404</v>
+        <v>4.5066</v>
       </c>
       <c r="I7" t="n">
         <v>4.5827</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8013</v>
+        <v>5.1356</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0225</v>
+        <v>2.1634</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5183</v>
+        <v>1.6021</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8013</v>
+        <v>5.1356</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8718</v>
+        <v>3.2061</v>
       </c>
       <c r="G8" t="n">
         <v>1.9295</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8718</v>
+        <v>3.2061</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8718</v>
+        <v>3.2061</v>
       </c>
       <c r="J8" t="n">
         <v>1.9295</v>
@@ -805,7 +805,7 @@
         <v>97</v>
       </c>
       <c r="M8" t="n">
-        <v>4.801299999999999</v>
+        <v>5.1356</v>
       </c>
       <c r="N8" t="n">
         <v>253</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4987</v>
+        <v>4.6582</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8951</v>
+        <v>1.9623</v>
       </c>
       <c r="D9" t="n">
-        <v>1.396</v>
+        <v>1.4119</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4987</v>
+        <v>4.6582</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0209</v>
+        <v>3.1804</v>
       </c>
       <c r="G9" t="n">
         <v>1.4778</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0209</v>
+        <v>3.1804</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4485</v>
+        <v>2.5778</v>
       </c>
       <c r="J9" t="n">
         <v>1.4778</v>
@@ -851,7 +851,7 @@
         <v>138</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9263</v>
+        <v>4.0556</v>
       </c>
       <c r="N9" t="n">
         <v>312</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.408</v>
+        <v>4.3886</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8569</v>
+        <v>1.8487</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3594</v>
+        <v>1.3045</v>
       </c>
       <c r="E10" t="n">
-        <v>4.408</v>
+        <v>4.3886</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0745</v>
+        <v>4.0551</v>
       </c>
       <c r="G10" t="n">
         <v>0.3335</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0858</v>
+        <v>4.0553</v>
       </c>
       <c r="I10" t="n">
         <v>4.1239</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9635</v>
+        <v>3.9487</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6696</v>
+        <v>1.6634</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1798</v>
+        <v>1.1293</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9635</v>
+        <v>3.9487</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9635</v>
+        <v>3.9487</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9635</v>
+        <v>3.9487</v>
       </c>
       <c r="I11" t="n">
         <v>3.982</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6036</v>
+        <v>3.7164</v>
       </c>
       <c r="C12" t="n">
-        <v>1.518</v>
+        <v>1.5655</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0344</v>
+        <v>1.0367</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6036</v>
+        <v>3.7164</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2413</v>
+        <v>2.3541</v>
       </c>
       <c r="G12" t="n">
         <v>1.3623</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2413</v>
+        <v>2.3541</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2413</v>
+        <v>2.3541</v>
       </c>
       <c r="J12" t="n">
         <v>1.3623</v>
@@ -989,7 +989,7 @@
         <v>97</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6036</v>
+        <v>3.7164</v>
       </c>
       <c r="N12" t="n">
         <v>253</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5179</v>
+        <v>3.5047</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4819</v>
+        <v>1.4763</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9998</v>
+        <v>0.9524</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5179</v>
+        <v>3.5047</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5179</v>
+        <v>3.5047</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5179</v>
+        <v>3.5047</v>
       </c>
       <c r="I13" t="n">
         <v>3.5342</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4899</v>
+        <v>3.4958</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4701</v>
+        <v>1.4726</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9885</v>
+        <v>0.9488</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4899</v>
+        <v>3.4958</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2292</v>
+        <v>3.6302</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2607</v>
+        <v>-0.1344</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2292</v>
+        <v>3.6302</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2292</v>
+        <v>3.6302</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2607</v>
+        <v>-0.1344</v>
       </c>
       <c r="K14" t="n">
         <v>164</v>
@@ -1081,7 +1081,7 @@
         <v>136</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4899</v>
+        <v>3.4958</v>
       </c>
       <c r="N14" t="n">
         <v>300</v>
@@ -1090,173 +1090,173 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3873</v>
+        <v>3.4899</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4269</v>
+        <v>1.4701</v>
       </c>
       <c r="D15" t="n">
-        <v>0.947</v>
+        <v>0.9465</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3873</v>
+        <v>3.4899</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2341</v>
+        <v>2.2292</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1532</v>
+        <v>1.2607</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2341</v>
+        <v>2.2292</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8108</v>
+        <v>2.2292</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1532</v>
+        <v>1.2607</v>
       </c>
       <c r="K15" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="L15" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M15" t="n">
-        <v>2.964</v>
+        <v>3.4899</v>
       </c>
       <c r="N15" t="n">
-        <v>312</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0171</v>
+        <v>3.3873</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2709</v>
+        <v>1.4269</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7975</v>
+        <v>0.9056</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0171</v>
+        <v>3.3873</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5052</v>
+        <v>2.2341</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4881</v>
+        <v>1.1532</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5052</v>
+        <v>2.2341</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5379</v>
+        <v>1.8108</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4881</v>
+        <v>1.1532</v>
       </c>
       <c r="K16" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L16" t="n">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0498</v>
+        <v>2.964</v>
       </c>
       <c r="N16" t="n">
-        <v>223</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8423</v>
+        <v>2.991</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1973</v>
+        <v>1.26</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7269</v>
+        <v>0.7477</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8423</v>
+        <v>2.991</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7082</v>
+        <v>3.4791</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1341</v>
+        <v>-0.4881</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7082</v>
+        <v>3.4791</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7082</v>
+        <v>3.5379</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1341</v>
+        <v>-0.4881</v>
       </c>
       <c r="K17" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="L17" t="n">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8423</v>
+        <v>3.0498</v>
       </c>
       <c r="N17" t="n">
-        <v>300</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6629</v>
+        <v>2.8423</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1217</v>
+        <v>1.1973</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6544</v>
+        <v>0.6885</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6629</v>
+        <v>2.8423</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7973</v>
+        <v>1.7082</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1344</v>
+        <v>1.1341</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7973</v>
+        <v>1.7082</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7973</v>
+        <v>1.7082</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1344</v>
+        <v>1.1341</v>
       </c>
       <c r="K18" t="n">
         <v>164</v>
@@ -1265,7 +1265,7 @@
         <v>136</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6629</v>
+        <v>2.8423</v>
       </c>
       <c r="N18" t="n">
         <v>300</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4791</v>
+        <v>2.4833</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0443</v>
+        <v>1.0461</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5454</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4791</v>
+        <v>2.4833</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8059</v>
+        <v>2.4833</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3268</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8059</v>
+        <v>2.4833</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8321</v>
+        <v>2.4833</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3268</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>273</v>
+        <v>154</v>
       </c>
       <c r="L19" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5053</v>
+        <v>2.4833</v>
       </c>
       <c r="N19" t="n">
-        <v>345</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1315</v>
+        <v>2.4582</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8979</v>
+        <v>1.0355</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4397</v>
+        <v>0.5354</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1315</v>
+        <v>2.4582</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1315</v>
+        <v>2.785</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3268</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1315</v>
+        <v>2.785</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1414</v>
+        <v>2.8321</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3268</v>
       </c>
       <c r="K20" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1414</v>
+        <v>2.5053</v>
       </c>
       <c r="N20" t="n">
-        <v>263</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0854</v>
+        <v>2.1235</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8945</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4211</v>
+        <v>0.4021</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0854</v>
+        <v>2.1235</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0854</v>
+        <v>2.1235</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0854</v>
+        <v>2.1235</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0854</v>
+        <v>2.1414</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>128</v>
+        <v>263</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0854</v>
+        <v>2.1414</v>
       </c>
       <c r="N21" t="n">
-        <v>128</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0618</v>
+        <v>2.0854</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8685</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4116</v>
+        <v>0.3869</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0618</v>
+        <v>2.0854</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0618</v>
+        <v>2.0854</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0618</v>
+        <v>2.0854</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0618</v>
+        <v>2.0854</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0618</v>
+        <v>2.0854</v>
       </c>
       <c r="N22" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
@@ -1468,7 +1468,7 @@
         <v>0.8657</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4089</v>
+        <v>0.3748</v>
       </c>
       <c r="E23" t="n">
         <v>2.0551</v>
@@ -1504,400 +1504,400 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8877</v>
+        <v>1.9229</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7952</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3412</v>
+        <v>0.3222</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8877</v>
+        <v>1.9229</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1033</v>
+        <v>1.9229</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2156</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1033</v>
+        <v>1.9229</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1229</v>
+        <v>1.9229</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2156</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="L24" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9073</v>
+        <v>1.9229</v>
       </c>
       <c r="N24" t="n">
-        <v>345</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8679</v>
+        <v>1.872</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.7886</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3332</v>
+        <v>0.3019</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8679</v>
+        <v>1.872</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6088</v>
+        <v>2.0876</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7409</v>
+        <v>-0.2156</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6088</v>
+        <v>2.0876</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6331</v>
+        <v>2.1229</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7409</v>
+        <v>-0.2156</v>
       </c>
       <c r="K25" t="n">
-        <v>175</v>
+        <v>273</v>
       </c>
       <c r="L25" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8922</v>
+        <v>1.9073</v>
       </c>
       <c r="N25" t="n">
-        <v>223</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.8221</v>
+        <v>1.8484</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7786</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3147</v>
+        <v>0.2925</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8221</v>
+        <v>1.8484</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8221</v>
+        <v>2.5893</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.7409</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8221</v>
+        <v>2.5893</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8221</v>
+        <v>2.6331</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.7409</v>
       </c>
       <c r="K26" t="n">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M26" t="n">
-        <v>1.8221</v>
+        <v>1.8922</v>
       </c>
       <c r="N26" t="n">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6654</v>
+        <v>1.8058</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7015</v>
+        <v>0.7607</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2514</v>
+        <v>0.2755</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6654</v>
+        <v>1.8058</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6654</v>
+        <v>3.1204</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1.3146</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6654</v>
+        <v>3.1204</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6654</v>
+        <v>2.5292</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1.3146</v>
       </c>
       <c r="K27" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6654</v>
+        <v>1.2146</v>
       </c>
       <c r="N27" t="n">
-        <v>177</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.546</v>
+        <v>1.6654</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6512</v>
+        <v>0.7015</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2032</v>
+        <v>0.2196</v>
       </c>
       <c r="E28" t="n">
-        <v>1.546</v>
+        <v>1.6654</v>
       </c>
       <c r="F28" t="n">
-        <v>1.546</v>
+        <v>1.6654</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.546</v>
+        <v>1.6654</v>
       </c>
       <c r="I28" t="n">
-        <v>1.546</v>
+        <v>1.6654</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.546</v>
+        <v>1.6654</v>
       </c>
       <c r="N28" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4903</v>
+        <v>1.5558</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6278</v>
+        <v>0.6554</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1807</v>
+        <v>0.1759</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4903</v>
+        <v>1.5558</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4903</v>
+        <v>1.5558</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4903</v>
+        <v>1.5558</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4903</v>
+        <v>1.5558</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4903</v>
+        <v>1.5558</v>
       </c>
       <c r="N29" t="n">
-        <v>177</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4892</v>
+        <v>1.5303</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6273</v>
+        <v>0.6446</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1802</v>
+        <v>0.1658</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4892</v>
+        <v>1.5303</v>
       </c>
       <c r="F30" t="n">
-        <v>2.8038</v>
+        <v>1.5303</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.3146</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.8038</v>
+        <v>1.5303</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2726</v>
+        <v>1.5303</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.3146</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="L30" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9580000000000002</v>
+        <v>1.5303</v>
       </c>
       <c r="N30" t="n">
-        <v>323</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>poizon</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4165</v>
+        <v>1.4903</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5967</v>
+        <v>0.6278</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1509</v>
+        <v>0.1498</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4165</v>
+        <v>1.4903</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4165</v>
+        <v>1.4903</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4165</v>
+        <v>1.4903</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4165</v>
+        <v>1.4903</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4165</v>
+        <v>1.4903</v>
       </c>
       <c r="N31" t="n">
-        <v>134</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SHiPZ</t>
+          <t>poizon</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3858</v>
+        <v>1.4165</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5838</v>
+        <v>0.5967</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1385</v>
+        <v>0.1204</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3858</v>
+        <v>1.4165</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3858</v>
+        <v>1.4165</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3858</v>
+        <v>1.4165</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3858</v>
+        <v>1.4165</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3858</v>
+        <v>1.4165</v>
       </c>
       <c r="N32" t="n">
         <v>134</v>
@@ -1918,216 +1918,216 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>SHiPZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3792</v>
+        <v>1.3858</v>
       </c>
       <c r="C33" t="n">
-        <v>0.581</v>
+        <v>0.5838</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1358</v>
+        <v>0.1082</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3792</v>
+        <v>1.3858</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9094</v>
+        <v>1.3858</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.5302</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.9094</v>
+        <v>1.3858</v>
       </c>
       <c r="I33" t="n">
-        <v>1.9272</v>
+        <v>1.3858</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5302</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="L33" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.397</v>
+        <v>1.3858</v>
       </c>
       <c r="N33" t="n">
-        <v>223</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0089</v>
+        <v>1.365</v>
       </c>
       <c r="C34" t="n">
-        <v>0.425</v>
+        <v>0.575</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0138</v>
+        <v>0.0999</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0089</v>
+        <v>1.365</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0089</v>
+        <v>1.8952</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.5302</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0089</v>
+        <v>1.8952</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0089</v>
+        <v>1.9272</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.5302</v>
       </c>
       <c r="K34" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0089</v>
+        <v>1.397</v>
       </c>
       <c r="N34" t="n">
-        <v>134</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9876</v>
+        <v>1.0089</v>
       </c>
       <c r="C35" t="n">
-        <v>0.416</v>
+        <v>0.425</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0224</v>
+        <v>-0.042</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9876</v>
+        <v>1.0089</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9876</v>
+        <v>1.0089</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9876</v>
+        <v>1.0089</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9876</v>
+        <v>1.0089</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9876</v>
+        <v>1.0089</v>
       </c>
       <c r="N35" t="n">
-        <v>177</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9728</v>
+        <v>0.9876</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4098</v>
+        <v>0.416</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0284</v>
+        <v>-0.0505</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9728</v>
+        <v>0.9876</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9728</v>
+        <v>0.9876</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9728</v>
+        <v>0.9876</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9728</v>
+        <v>0.9876</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9728</v>
+        <v>0.9876</v>
       </c>
       <c r="N36" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9394</v>
+        <v>0.9728</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3957</v>
+        <v>0.4098</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0419</v>
+        <v>-0.0563</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9394</v>
+        <v>0.9728</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9394</v>
+        <v>0.9728</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9394</v>
+        <v>0.9728</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9394</v>
+        <v>0.9728</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9394</v>
+        <v>0.9728</v>
       </c>
       <c r="N37" t="n">
         <v>204</v>
@@ -2148,507 +2148,507 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8137</v>
+        <v>0.9394</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3428</v>
+        <v>0.3957</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0926</v>
+        <v>-0.0697</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8137</v>
+        <v>0.9394</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8137</v>
+        <v>0.9394</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8137</v>
+        <v>0.9394</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8137</v>
+        <v>0.9394</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8137</v>
+        <v>0.9394</v>
       </c>
       <c r="N38" t="n">
-        <v>128</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7618</v>
+        <v>0.9169</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3209</v>
+        <v>0.3862</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1136</v>
+        <v>-0.0786</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7618</v>
+        <v>0.9169</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7618</v>
+        <v>1.6093</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.6924</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7618</v>
+        <v>1.6093</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7618</v>
+        <v>1.3044</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.6924</v>
       </c>
       <c r="K39" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7618</v>
+        <v>0.612</v>
       </c>
       <c r="N39" t="n">
-        <v>154</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7482</v>
+        <v>0.8137</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3152</v>
+        <v>0.3428</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1191</v>
+        <v>-0.1197</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7482</v>
+        <v>0.8137</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7482</v>
+        <v>0.8137</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7482</v>
+        <v>0.8137</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7482</v>
+        <v>0.8137</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7482</v>
+        <v>0.8137</v>
       </c>
       <c r="N40" t="n">
-        <v>177</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6954</v>
+        <v>0.7482</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2929</v>
+        <v>0.3152</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1404</v>
+        <v>-0.1458</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6954</v>
+        <v>0.7482</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3878</v>
+        <v>0.7482</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6924</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.3878</v>
+        <v>0.7482</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1248</v>
+        <v>0.7482</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6924</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L41" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4324</v>
+        <v>0.7482</v>
       </c>
       <c r="N41" t="n">
-        <v>312</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6907</v>
+        <v>0.6916</v>
       </c>
       <c r="C42" t="n">
-        <v>0.291</v>
+        <v>0.2913</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1423</v>
+        <v>-0.1684</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6907</v>
+        <v>0.6916</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5971</v>
+        <v>0.6916</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0936</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5971</v>
+        <v>0.6916</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5971</v>
+        <v>0.6916</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0936</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L42" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6907</v>
+        <v>0.6916</v>
       </c>
       <c r="N42" t="n">
-        <v>253</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6646</v>
+        <v>0.6907</v>
       </c>
       <c r="C43" t="n">
-        <v>0.28</v>
+        <v>0.291</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1529</v>
+        <v>-0.1687</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6646</v>
+        <v>0.6907</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6646</v>
+        <v>0.5971</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.0936</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6646</v>
+        <v>0.5971</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6677</v>
+        <v>0.5971</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.0936</v>
       </c>
       <c r="K43" t="n">
-        <v>263</v>
+        <v>156</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6677</v>
+        <v>0.6907</v>
       </c>
       <c r="N43" t="n">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vice</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3931</v>
+        <v>0.6621</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1656</v>
+        <v>0.2789</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2626</v>
+        <v>-0.1801</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3931</v>
+        <v>0.6621</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3931</v>
+        <v>0.6621</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3931</v>
+        <v>0.6621</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3931</v>
+        <v>0.6677</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>95</v>
+        <v>263</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3931</v>
+        <v>0.6677</v>
       </c>
       <c r="N44" t="n">
-        <v>95</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3869</v>
+        <v>0.4279</v>
       </c>
       <c r="C45" t="n">
-        <v>0.163</v>
+        <v>0.1803</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2651</v>
+        <v>-0.2734</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3869</v>
+        <v>0.4279</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3869</v>
+        <v>1.7463</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1.3184</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3869</v>
+        <v>1.7463</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3869</v>
+        <v>1.4154</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1.3184</v>
       </c>
       <c r="K45" t="n">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3869</v>
+        <v>0.09699999999999998</v>
       </c>
       <c r="N45" t="n">
-        <v>74</v>
+        <v>323</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>vice</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.377</v>
+        <v>0.3931</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1588</v>
+        <v>0.1656</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2691</v>
+        <v>-0.2873</v>
       </c>
       <c r="E46" t="n">
-        <v>0.377</v>
+        <v>0.3931</v>
       </c>
       <c r="F46" t="n">
-        <v>0.377</v>
+        <v>0.3931</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.377</v>
+        <v>0.3931</v>
       </c>
       <c r="I46" t="n">
-        <v>0.377</v>
+        <v>0.3931</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.377</v>
+        <v>0.3931</v>
       </c>
       <c r="N46" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3288</v>
+        <v>0.3895</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1385</v>
+        <v>0.1641</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2885</v>
+        <v>-0.2887</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3288</v>
+        <v>0.3895</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3288</v>
+        <v>0.3895</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3288</v>
+        <v>0.3895</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3288</v>
+        <v>0.3895</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3288</v>
+        <v>0.3895</v>
       </c>
       <c r="N47" t="n">
-        <v>204</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2174</v>
+        <v>0.3386</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0916</v>
+        <v>0.1426</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3335</v>
+        <v>-0.309</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2174</v>
+        <v>0.3386</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5358</v>
+        <v>0.3386</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.3184</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5358</v>
+        <v>0.3386</v>
       </c>
       <c r="I48" t="n">
-        <v>1.2448</v>
+        <v>0.3386</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.3184</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="L48" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.07360000000000011</v>
+        <v>0.3386</v>
       </c>
       <c r="N48" t="n">
-        <v>323</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49">
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2015</v>
+        <v>0.1958</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0849</v>
+        <v>0.0825</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.34</v>
+        <v>-0.3659</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2015</v>
+        <v>0.1958</v>
       </c>
       <c r="F49" t="n">
-        <v>0.775</v>
+        <v>0.7693</v>
       </c>
       <c r="G49" t="n">
         <v>-0.5735</v>
       </c>
       <c r="H49" t="n">
-        <v>0.775</v>
+        <v>0.7693</v>
       </c>
       <c r="I49" t="n">
         <v>0.7823</v>
@@ -2710,7 +2710,7 @@
         <v>0.0299</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3927</v>
+        <v>-0.4157</v>
       </c>
       <c r="E50" t="n">
         <v>0.0709</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0477</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4671</v>
+        <v>-0.489</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1133</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1714</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5857</v>
+        <v>-0.606</v>
       </c>
       <c r="E52" t="n">
         <v>-0.4068</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.4566</v>
+        <v>-0.4606</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1923</v>
+        <v>-0.194</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6058</v>
+        <v>-0.6274</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.4566</v>
+        <v>-0.4606</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5434</v>
+        <v>0.5394</v>
       </c>
       <c r="G53" t="n">
         <v>-1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5434</v>
+        <v>0.5394</v>
       </c>
       <c r="I53" t="n">
         <v>0.5485</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.4767</v>
+        <v>-0.4756</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2008</v>
+        <v>-0.2003</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6139</v>
+        <v>-0.6334</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4767</v>
+        <v>-0.4756</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1462</v>
+        <v>-0.1451</v>
       </c>
       <c r="G54" t="n">
         <v>-0.3305</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1462</v>
+        <v>-0.1451</v>
       </c>
       <c r="I54" t="n">
         <v>-0.1476</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2051</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6181</v>
+        <v>-0.6379</v>
       </c>
       <c r="E55" t="n">
         <v>-0.487</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2232</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6354</v>
+        <v>-0.655</v>
       </c>
       <c r="E56" t="n">
         <v>-0.5298</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2485</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6597</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5899</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2725</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6827</v>
+        <v>-0.7016</v>
       </c>
       <c r="E58" t="n">
         <v>-0.6469</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2747</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6848</v>
+        <v>-0.7037</v>
       </c>
       <c r="E59" t="n">
         <v>-0.652</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2799</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6898</v>
+        <v>-0.7086</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6645</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3083</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.717</v>
+        <v>-0.7355</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7319</v>
@@ -3262,7 +3262,7 @@
         <v>-0.337</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7446</v>
+        <v>-0.7627</v>
       </c>
       <c r="E62" t="n">
         <v>-0.8001</v>
@@ -3308,7 +3308,7 @@
         <v>-0.3648</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7712</v>
+        <v>-0.7889</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8659</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3863</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.8092</v>
       </c>
       <c r="E64" t="n">
         <v>-0.917</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4279</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8318</v>
+        <v>-0.8486</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0159</v>
@@ -3446,7 +3446,7 @@
         <v>-0.465</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8673</v>
+        <v>-0.8837</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1039</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4802</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8819</v>
+        <v>-0.8981</v>
       </c>
       <c r="E67" t="n">
         <v>-1.14</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4902</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8915</v>
+        <v>-0.9075</v>
       </c>
       <c r="E68" t="n">
         <v>-1.1637</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5789</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9765</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3743</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5848</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9822</v>
+        <v>-0.997</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3883</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5869</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9842</v>
+        <v>-0.999</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3932</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5893</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9865</v>
+        <v>-1.0013</v>
       </c>
       <c r="E72" t="n">
         <v>-1.399</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6601</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0544</v>
+        <v>-1.0682</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5671</v>
@@ -3814,7 +3814,7 @@
         <v>-0.662</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0562</v>
+        <v>-1.07</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5715</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.5827</v>
+        <v>-1.5768</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6667</v>
+        <v>-0.6642</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0607</v>
+        <v>-1.0721</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.5827</v>
+        <v>-1.5768</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.5827</v>
+        <v>-1.5768</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.5827</v>
+        <v>-1.5768</v>
       </c>
       <c r="I75" t="n">
         <v>-1.5901</v>
@@ -3906,7 +3906,7 @@
         <v>-0.6994</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0921</v>
+        <v>-1.1054</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6603</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7826</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1719</v>
+        <v>-1.1841</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8578</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9016999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2861</v>
+        <v>-1.2967</v>
       </c>
       <c r="E78" t="n">
         <v>-2.1406</v>
@@ -4044,7 +4044,7 @@
         <v>-1.0217</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4012</v>
+        <v>-1.4102</v>
       </c>
       <c r="E79" t="n">
         <v>-2.4255</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0384</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4172</v>
+        <v>-1.426</v>
       </c>
       <c r="E80" t="n">
         <v>-2.4651</v>
@@ -4136,7 +4136,7 @@
         <v>-1.3209</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6881</v>
+        <v>-1.6932</v>
       </c>
       <c r="E81" t="n">
         <v>-3.1357</v>
